--- a/Dokumente/Dhampir-Datenbank.xlsx
+++ b/Dokumente/Dhampir-Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7615D72B-43D6-46BD-BDC5-4A06D6FC3D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADDA1A8-6E48-482D-BE58-7D7896A9740C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -279,9 +279,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, was bei seinen Nachforschungen und Missionen hilfreich sein kann, da er so mit Ihnen (den Toten) kommuniziert und Sie beherrschen kann. 
+      <t xml:space="preserve">, was bei seinen Nachforschungen und Missionen hilfreich sein kann, da er so mit Ihnen (den Toten) kommuniziert und Sie beherrschen kann. 
 Er ist aber auch in dieser Gestalt etwas einzigartiges, weil er Dinge entdeckt die andere seine Art nie wahrnehmen konnten und übertrifft in Mächtigkeit an Kraft alle bekannten Vampire der Stufe 3. Als Dhampir ist er so ein entschiedener Feind der Vampire
- aus der Dritten Generation und wird von diesen, nach einer Sichtung gnadenlos gejagt.</t>
+ aus der Dritten Generation und wird von diesen, nach einer Sichtung gnadenlos gejagt.
+Akt 1: </t>
     </r>
   </si>
 </sst>
@@ -562,19 +563,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -890,20 +891,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
       <c r="M2" s="1"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -955,7 +956,7 @@
       <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="19" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="9"/>
@@ -980,7 +981,7 @@
     <row r="6" spans="1:21" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="20" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="10"/>
@@ -1005,7 +1006,7 @@
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="22"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1028,7 +1029,7 @@
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="22"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -1051,7 +1052,7 @@
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
@@ -1074,7 +1075,7 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="22"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -1097,7 +1098,7 @@
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="22"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -1120,7 +1121,7 @@
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="10"/>
-      <c r="C12" s="22"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -1143,7 +1144,7 @@
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="22"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1166,7 +1167,7 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="22"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
@@ -1189,7 +1190,7 @@
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="22"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1212,7 +1213,7 @@
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="22"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -1235,7 +1236,7 @@
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="10"/>
-      <c r="C17" s="22"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
@@ -1258,7 +1259,7 @@
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="10"/>
-      <c r="C18" s="22"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -1281,7 +1282,7 @@
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="22"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -2020,146 +2021,146 @@
     </row>
     <row r="51" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:21" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
     </row>
     <row r="53" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="20"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
     </row>
     <row r="54" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="19"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="19"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="19"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="19"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="19"/>
-      <c r="J64" s="19"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
     </row>
     <row r="65" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Dokumente/Dhampir-Datenbank.xlsx
+++ b/Dokumente/Dhampir-Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADDA1A8-6E48-482D-BE58-7D7896A9740C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A65B9E-025F-46E3-953B-F138F43325BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Bruderschaft der Dhampire</t>
   </si>
@@ -60,7 +60,250 @@
     <t>Lager der Vampire</t>
   </si>
   <si>
-    <t>Basim überlebte seine Kindheit durch Schlauheit und das, was andere wegwarfen. Tagsüber leerte er mit seiner Freundin Nihal den Leuten dier Taschen, des nachts quäte ein furchterregender Dschinn, den Schlaf des jungen Straßendiebes.
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Daniel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Als Schüler der Oberstufe, stach Daniel als Schüler bisher nur durch seine schnelle Auffassungsgabe und cooler Sportler hervor, aber unter seinen Schüler das ein oder andere Mal als Klassenclown und "Beschützer der entrechteten Kinder". Aber schon seit frühester Kindheit kam in ihm das Gefühl auf das etwas mit ihm und seinen Körper nicht stimmte, was sich bis in seine Träume fraß und ihn fantastische Reiche aus fernen Zeiten zeigte, was ihn ums ein oder andere Mal den Schlaf, sowie die Kraft raubte. Er wachte nach diesen Träumen immer mit Tränen und Trauer über das verlorene, was er nicht kannte auf und wurde von seinem treuen Haustier, seiner Fledermaus "Sebastian" getröstet um in den nächsten Tag zu finden. Ehrgeizig und von den Wunsch getrieben, die Lösung nach diesem inneren Wunsch zu finden, aber auch durch einen eisernen Willen getrieben, sehnte sich Dani danach, die Tage bis zu dem Zeitpunkt zu durchleben, anderem sich die Lösung für alle zeigen Würde.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Prolog: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nachdem Daniel bei einer Schlägerei in seiner Schule etwas Blut von einem Mitschüler in seinem Mund bekam, änderte sich sein Körper rapide. Anders als bei "normalen" Menschen wahr das Blut nicht unverträglich für ihn, sondern bewirkte das sich sein Körper veränderte &gt; seine Muskeln begannen sich anzuspannen und er konnte in einem Spiegel erkennen das sich seine Blonden Haare und Blauen Augen, in einen dunklen, fast schwarzen Ton umwandelten, seine Augen stachen dunkelorange hervor 
+und sein Gebiss wurde gerade, sowie die Schneidezähne wurden spitzer. Nach einer abenteuerlichen Reise, bei der eine Reizüberflutung durch seine geschärften Sinne erlebte, erfuhr er daheim durch diese neue Gabe das ihn seine Eltern, 
+bisher all die Jahre verschwiegen hatten, das seine Herkunft unbekannt ist und er schon als Baby vieles unglaubliche bewirkt und erlebt hatte. Nach einem Treffen mit seiner Freundin Jessica und den Angriff durch Vampire (den er gewann) geriet er in eine vollkommen neue Welt, hinter der bisherigen Welt; die sein Stadtbild grundlegend veränderte. Damit endete der Auftakt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dani(el) als Dhampir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Als Dhampir, hat er zu seinem veränderten Aussehen, auch geschärfte Sinne (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sehen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Er kann mehr als 1 km klar sehen; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hören</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Durch die dicksten Wände kann er alles wahrnehmen, er braucht sich nur zu fokussieren; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Riechen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Wahrnehmung aller Düfte in der Umgebung, bis zu 500 m (Konzentration ist alles), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Schmecken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Selbst kleinste Geschmacksnuancen werden Wahrgenommen, bis zu exakten Eisengehalt im Blut und </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tastsinn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Sämtliche Arten der Berührung werden wahrgenommen und bei Gefahr abgewehrt) und neue Sinne die er als Mensch nicht hat wie der </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Aura Sinn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, indem er Feinde sichten kann und die </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nekromantie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, was bei seinen Nachforschungen und Missionen hilfreich sein kann, da er so mit Ihnen (den Toten) kommuniziert und Sie beherrschen kann. 
+Er ist aber auch in dieser Gestalt etwas einzigartiges, weil er Dinge entdeckt die andere seine Art nie wahrnehmen konnten und übertrifft in Mächtigkeit an Kraft alle bekannten Vampire der Stufe 3. Als Dhampir ist er so ein entschiedener Feind der Vampire
+ aus der Dritten Generation und wird von diesen, nach einer Sichtung gnadenlos gejagt.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Als Daniel auf seinen ersten Einsatz zur Unterstützung etwas Blut zu sich nimmt, merkt er noch einen weiteren Vorteil. Er wird kurzzeitig für Vampire unsichtbar und ist auch viel schneller als die niederen, bis er in einen rein rennt. Aber auch gegen die Ghule die in auf der Suche nach den entführten begegneten konnte er so mit Leichtigkeit besiegen, was ihn zusätzliche Motivation bescherte. Nach seiner erste Mission bekann dadurch schließlich auch die Suche nach der Art der Möglichkeiten die in seiner Dhampir-Gestalt verursachen kann.</t>
+    </r>
+  </si>
+  <si>
+    <t>Basim überlebte seine Kindheit durch Schlauheit und das, was andere wegwarfen. Tagsüber leerte er mit seiner Freundin Nihal den Leuten dir Taschen, des nachts quälte ein furchterregender Dschinn, den Schlaf des jungen Straßendiebes.
 Ehrgeizig und von dem Wunsch getrieben, der Gerechtigkeit zu dienen, sehnte sich Basim danach, ein Verborgener zu werden. Je näher er jedoch seinem Traum kam, desto näher kam auch sein Nachtmahr.</t>
   </si>
   <si>
@@ -73,7 +316,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Daniel</t>
+      <t>Dani(el) als Vampir</t>
     </r>
     <r>
       <rPr>
@@ -84,7 +327,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Als Schüler der Oberstufe, stach Daniel als Schüler bisher nur durch seine schnelle Auffassungsgabe und cooler Sportler hervor, aber unter seinen Schüler das ein oder andere Mal als Klassenclown und "Beschützer der entrechteten Kinder". Aber schon seit frühester Kindheit kam in ihm das Gefühl auf das etwas mit ihm und seinen Körper nicht stimmte, was sich bis in seine Träume frass und ihn fantastische Reiche aus fernen Zeiten zeigte, was ihn ums ein oder andere Mal den Schlaf, sowie die Kraft raubte. Er wachte nach diesen Träumen immer mit Tränen und Trauer über das verlorene, was er nicht kannte auf und wurde von seinem treuen Haustier, seiner Fledermaus "Sebastian" getröstet um in den nächsten Tag zu finden. Ehrgeizig und von den Wunsch getrieben, die Lösung nach diesem inneren Wunsch zu finden, aber auch durch einen eisernen Willen getrieben, sehnte sich Dani danach, die Tage bis zu dem Zeitpunkt zu durchleben, andem sich die Lösung für alle zeigen Würde.
+In seiner Vampirgestalt ist sein Charakter sehr aufbrausend, blutdurstig und kaum kontrollierbar. Durch seine noch weiter geschärften Sinne und Muskelkraft kann er sehr schnell potenzielle Opfer (Nicht-Menschliche und Menschliche) erreichen und diese aufnehmen, ohne das Überreste bleiben. Diese Gestalt erreicht er, wen er seinen Körper zuviel Blut zufügt, was das Team dazu brachte mehr über diese Seite an ihm zu erforsch und vielleicht in Zukunft zu beherrschen. Man konnte aber schon bei den ersten Tests erkennen das er in dieser Gestalt andere Wesen einnehmen und seinem  Willen unterwerfen kann, was für kommende Missionen, interessante Verwendungsweisen wären.
 </t>
     </r>
     <r>
@@ -96,19 +339,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Prolog: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Nachdem Daniel bei einer Schlägerei in seiner Schule etwas Blut von einem Mitschüler in seinem Mund bekam, änderte sich sein Körper rapide. Anders als bei "normalen" Menschen wahr das Blut nicht unverträglich für ihn, sondern bewirkte das sich sein Körper veränderte &gt; seine Muskeln begannen sich anzuspannen und er konnte in einem Spiegel erkennen das sich seine Blonden Haare und Blauen Augen, in einen dunklen, fast schwarzen Ton umwandelten, seine Augen stachen dunkelorange hervor 
-und sein Gebiss wurde gerade, sowie die Schneidezähne wurden spitzer. Nach einer abenteuerlichen Reise, bei der eine Reizüberflutung durch seine geschärtften Sinne erlebte, erfuhr er daheim durch diese neue Gabe das ihn seine Eltern, 
-bisher all die Jahre verschwiegern hatten, das seine Herkunft unbekannt ist und er schon als Baby vieles unglaubliche bewirkt und erlebt hatte. Nach einem Treffen mit seiner Freundin Jessica und den Angriff durch Vampire (den er gewann) geritt er in eine vollkommen neue Welt, hinter der bisherigen Welt; die sein Stadtbild grundlegend veränderte. Damit endete der Auftakt.</t>
+      <t>Akt 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Das letzte was er von Akt 13 noch wahr nahm, das ihn auf seinem Heimweg ein kalter Lufthauch und die Gier nach Blut erheilte, nun findet er sich in einem alten Gemäuer eines Gebäudes des Balkan wieder. Seiner Versuche aus diesem Labyrinth waren bislang nich von Erfolg gekrönt und machen ihn nur hoffnungsloser. Gerade hatte man sich als Team zusammengefunden, aber nun war er hier allein mit seinen Erzfeinden, mit denen er wenigstens wie in einem Art Bootcamp trainieren konnte.</t>
     </r>
   </si>
   <si>
@@ -121,7 +362,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Dani(el) als Dhampir</t>
+      <t>Sebastian die Fledermaus</t>
     </r>
     <r>
       <rPr>
@@ -132,7 +373,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-Als Dhampir, hat er zu seinem veränderten Aussehen, auch geschärfte Sinne (</t>
+Schon als Kleinkind fand er (laut seiner Eltern) eine Babyfledermaus, die er aufzog und die seit jeher ein festes Band der Verbundenheit eint. Aufgrund seiner Gabe die er im Prolog entdeckte, kann er mit seinem Begleiter kommunizieren, wobei ihn "Sebi" beim observieren der Missionsstandorte hilft, ihn aber auch in mancher brenzliger Situation, vor den Feinden rettet. Daniel und seinem Haustier eint dabei das verlangen herauszufinden woher und was Sie sind, den auch Sebi zeigt eine Veränderung wen er Blut aufnimmt, wie man beobachten konnte. So konnte man erkennen das hinter seiner putzigen Gestalt sich ein besonderes Geheimnis verbirgt.
+</t>
     </r>
     <r>
       <rPr>
@@ -143,146 +385,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Sehen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Er kann mehr als 1 km klar sehen; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hören</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Durch die dicksten Wände kann er alles wahrnehmen, er braucht sich nur zu fokussieren; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Riechen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Wahrnehmung aller Düfte in der Umgebung, bis zu 500 m (Konzentration ist alles), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Schmecken</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Selbst kleinste Geschmacksnuancen werden Wahrgenommen, bis zu exakten Eisengehalt im Blut und </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tastsinn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Sämtliche Arten der Berührung werden wahrgenommen und bei Gefahr abgewehrt) und neue Sinne die er als Mensch nicht hat wie der </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Aurasinn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, indem er Feinde sichten kann und die </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Nekromantie</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, was bei seinen Nachforschungen und Missionen hilfreich sein kann, da er so mit Ihnen (den Toten) kommuniziert und Sie beherrschen kann. 
-Er ist aber auch in dieser Gestalt etwas einzigartiges, weil er Dinge entdeckt die andere seine Art nie wahrnehmen konnten und übertrifft in Mächtigkeit an Kraft alle bekannten Vampire der Stufe 3. Als Dhampir ist er so ein entschiedener Feind der Vampire
- aus der Dritten Generation und wird von diesen, nach einer Sichtung gnadenlos gejagt.
-Akt 1: </t>
+      <t>Akt 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Eingesperrt in einer Tropfsteinhöhle kann nur er seine Kumpanen und besten Freund retten, die Fledermaus "Sebastian". Zeige dein ganzes Können in dieser besonderen Gestalt. Seine ersten Auswegsversuche waren dabei zwar armselig, aber er gibt immer Erfolge, wen man an Sie glaubt.</t>
     </r>
   </si>
 </sst>
@@ -957,7 +1070,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -978,11 +1091,11 @@
       <c r="T5" s="9"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="1:21" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="10"/>
       <c r="C6" s="20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1003,10 +1116,12 @@
       <c r="T6" s="10"/>
       <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="20" t="s">
+        <v>13</v>
+      </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
@@ -1026,10 +1141,12 @@
       <c r="T7" s="10"/>
       <c r="U7" s="5"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
@@ -2022,7 +2139,7 @@
     <row r="51" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:21" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="22" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>

--- a/Dokumente/Dhampir-Datenbank.xlsx
+++ b/Dokumente/Dhampir-Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A65B9E-025F-46E3-953B-F138F43325BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE08B90F-A66D-4ED8-A7BF-9D7B0CD6A1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Bruderschaft der Dhampire</t>
   </si>
@@ -362,7 +362,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Sebastian die Fledermaus</t>
+      <t>Sebastian, die Fledermaus</t>
     </r>
     <r>
       <rPr>
@@ -396,6 +396,52 @@
         <scheme val="minor"/>
       </rPr>
       <t>: Eingesperrt in einer Tropfsteinhöhle kann nur er seine Kumpanen und besten Freund retten, die Fledermaus "Sebastian". Zeige dein ganzes Können in dieser besonderen Gestalt. Seine ersten Auswegsversuche waren dabei zwar armselig, aber er gibt immer Erfolge, wen man an Sie glaubt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jessica, die dunkle Werwolfbraut</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Im Kindergarten lernte Sie den etwas verschlossenen Daniel kennen, der immer schon etwas anders war. Obwohl nur ein paar Monate jünger als Sie, entwickelt sich schon da ein "Große Schwester" empfinden zu ihm. Als Sie schließlich herausfand, das Sie zu einem Werwolfclan (ihr Vater ist der Werlord der Region) gehört und als deren Erbe ergoren ist, wurde Sie angewissen ihren besten Freund aus zuspionieren und notfalls umzubringen, wen er zur Gefahr für die "Anderwelt" (Welt der Mischwesen) werden würde, wie andere seiner Wesensart vor ihm. Um dies zu verhindern und ihn zu beschützen, schafft Sie mit ihm aber ein Team zusammen, was mit ihren unterschiedlichen Stärken, diese Aufgabe abwenden soll und Daniel in eine Richtung die ihm zum Beschützer der Anderwelt macht.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nach Daniels Rückkehr im Rheinland kommt der Werwolfclan zur Entscheidung, sein Leben als Opfer für ihren Wergott zu opfern. Jessica entscheidet daraufhin, den Clan zu verlassen und gemeinsam mit den Rittern den Sie angehört, dieses Opfer zu verhindern, um weiter mit Daniel nach den Fragen der Herkunft, Aufgabe und Zukunftsherausforderungen zu suchen.</t>
     </r>
   </si>
 </sst>
@@ -1166,10 +1212,12 @@
       <c r="T8" s="10"/>
       <c r="U8" s="5"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="105.75" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="20"/>
+      <c r="C9" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>

--- a/Dokumente/Dhampir-Datenbank.xlsx
+++ b/Dokumente/Dhampir-Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE08B90F-A66D-4ED8-A7BF-9D7B0CD6A1E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717BDA4F-5029-455D-B5BC-DB8843161AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Bruderschaft der Dhampire</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Gegnertypen (9)</t>
   </si>
   <si>
-    <t>Basis der Ritter der Nacht</t>
-  </si>
-  <si>
     <t>Die Ritter der Nacht</t>
   </si>
   <si>
@@ -303,8 +300,196 @@
     </r>
   </si>
   <si>
-    <t>Basim überlebte seine Kindheit durch Schlauheit und das, was andere wegwarfen. Tagsüber leerte er mit seiner Freundin Nihal den Leuten dir Taschen, des nachts quälte ein furchterregender Dschinn, den Schlaf des jungen Straßendiebes.
-Ehrgeizig und von dem Wunsch getrieben, der Gerechtigkeit zu dienen, sehnte sich Basim danach, ein Verborgener zu werden. Je näher er jedoch seinem Traum kam, desto näher kam auch sein Nachtmahr.</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sebastian, die Fledermaus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Schon als Kleinkind fand er (laut seiner Eltern) eine Babyfledermaus, die er aufzog und die seit jeher ein festes Band der Verbundenheit eint. Aufgrund seiner Gabe die er im Prolog entdeckte, kann er mit seinem Begleiter kommunizieren, wobei ihn "Sebi" beim observieren der Missionsstandorte hilft, ihn aber auch in mancher brenzliger Situation, vor den Feinden rettet. Daniel und seinem Haustier eint dabei das verlangen herauszufinden woher und was Sie sind, den auch Sebi zeigt eine Veränderung wen er Blut aufnimmt, wie man beobachten konnte. So konnte man erkennen das hinter seiner putzigen Gestalt sich ein besonderes Geheimnis verbirgt.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Eingesperrt in einer Tropfsteinhöhle kann nur er seine Kumpanen und besten Freund retten, die Fledermaus "Sebastian". Zeige dein ganzes Können in dieser besonderen Gestalt. Seine ersten Auswegsversuche waren dabei zwar armselig, aber er gibt immer Erfolge, wen man an Sie glaubt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jessica, die dunkle Werwolfbraut</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Im Kindergarten lernte Sie den etwas verschlossenen Daniel kennen, der immer schon etwas anders war. Obwohl nur ein paar Monate jünger als Sie, entwickelt sich schon da ein "Große Schwester" empfinden zu ihm. Als Sie schließlich herausfand, das Sie zu einem Werwolfclan (ihr Vater ist der Werlord der Region) gehört und als deren Erbe ergoren ist, wurde Sie angewissen ihren besten Freund aus zuspionieren und notfalls umzubringen, wen er zur Gefahr für die "Anderwelt" (Welt der Mischwesen) werden würde, wie andere seiner Wesensart vor ihm. Um dies zu verhindern und ihn zu beschützen, schafft Sie mit ihm aber ein Team zusammen, was mit ihren unterschiedlichen Stärken, diese Aufgabe abwenden soll und Daniel in eine Richtung die ihm zum Beschützer der Anderwelt macht.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nach Daniels Rückkehr im Rheinland kommt der Werwolfclan zur Entscheidung, sein Leben als Opfer für ihren Wergott zu opfern. Jessica entscheidet daraufhin, den Clan zu verlassen und gemeinsam mit den Rittern den Sie angehört, dieses Opfer zu verhindern, um weiter mit Daniel nach den Fragen der Herkunft, Aufgabe und Zukunftsherausforderungen zu suchen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Utz, der Mediziner und grüne Hexer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A
+Akt 1: </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thutmosis, der Ägyptologe und dunkle Hexer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A
+Akt 3:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jan, der Geschichtsstudent und Púcca</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A
+Akt 6:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sabrina, die Stadtbeamtin und Sirene</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+A
+Akt 12:</t>
+    </r>
   </si>
   <si>
     <r>
@@ -349,100 +534,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Das letzte was er von Akt 13 noch wahr nahm, das ihn auf seinem Heimweg ein kalter Lufthauch und die Gier nach Blut erheilte, nun findet er sich in einem alten Gemäuer eines Gebäudes des Balkan wieder. Seiner Versuche aus diesem Labyrinth waren bislang nich von Erfolg gekrönt und machen ihn nur hoffnungsloser. Gerade hatte man sich als Team zusammengefunden, aber nun war er hier allein mit seinen Erzfeinden, mit denen er wenigstens wie in einem Art Bootcamp trainieren konnte.</t>
+      <t>: Das letzte was er von Akt 13 noch wahr nahm, das ihn auf seinem Heimweg ein kalter Lufthauch und die Gier nach Blut ereilte, nun findet er sich in einem alten Gemäuer eines Gebäudes des Balkan wieder. Seiner Versuche aus diesem Labyrinth waren bislang nich von Erfolg gekrönt und machen ihn nur hoffnungsloser. Gerade hatte man sich als Team zusammengefunden, aber nun war er hier allein mit seinen Erzfeinden, mit denen er wenigstens wie in einem Art Bootcamp trainieren konnte.</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sebastian, die Fledermaus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Schon als Kleinkind fand er (laut seiner Eltern) eine Babyfledermaus, die er aufzog und die seit jeher ein festes Band der Verbundenheit eint. Aufgrund seiner Gabe die er im Prolog entdeckte, kann er mit seinem Begleiter kommunizieren, wobei ihn "Sebi" beim observieren der Missionsstandorte hilft, ihn aber auch in mancher brenzliger Situation, vor den Feinden rettet. Daniel und seinem Haustier eint dabei das verlangen herauszufinden woher und was Sie sind, den auch Sebi zeigt eine Veränderung wen er Blut aufnimmt, wie man beobachten konnte. So konnte man erkennen das hinter seiner putzigen Gestalt sich ein besonderes Geheimnis verbirgt.
+    <t xml:space="preserve">Basis der Ritter der Nacht
 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Akt 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Eingesperrt in einer Tropfsteinhöhle kann nur er seine Kumpanen und besten Freund retten, die Fledermaus "Sebastian". Zeige dein ganzes Können in dieser besonderen Gestalt. Seine ersten Auswegsversuche waren dabei zwar armselig, aber er gibt immer Erfolge, wen man an Sie glaubt.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jessica, die dunkle Werwolfbraut</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Im Kindergarten lernte Sie den etwas verschlossenen Daniel kennen, der immer schon etwas anders war. Obwohl nur ein paar Monate jünger als Sie, entwickelt sich schon da ein "Große Schwester" empfinden zu ihm. Als Sie schließlich herausfand, das Sie zu einem Werwolfclan (ihr Vater ist der Werlord der Region) gehört und als deren Erbe ergoren ist, wurde Sie angewissen ihren besten Freund aus zuspionieren und notfalls umzubringen, wen er zur Gefahr für die "Anderwelt" (Welt der Mischwesen) werden würde, wie andere seiner Wesensart vor ihm. Um dies zu verhindern und ihn zu beschützen, schafft Sie mit ihm aber ein Team zusammen, was mit ihren unterschiedlichen Stärken, diese Aufgabe abwenden soll und Daniel in eine Richtung die ihm zum Beschützer der Anderwelt macht.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Akt 16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Nach Daniels Rückkehr im Rheinland kommt der Werwolfclan zur Entscheidung, sein Leben als Opfer für ihren Wergott zu opfern. Jessica entscheidet daraufhin, den Clan zu verlassen und gemeinsam mit den Rittern den Sie angehört, dieses Opfer zu verhindern, um weiter mit Daniel nach den Fragen der Herkunft, Aufgabe und Zukunftsherausforderungen zu suchen.</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -669,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -736,6 +833,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,7 +1129,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="229.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1083,7 +1186,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>4</v>
@@ -1112,11 +1215,11 @@
     </row>
     <row r="5" spans="1:21" ht="166.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="9" t="s">
-        <v>7</v>
+      <c r="B5" s="23" t="s">
+        <v>18</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -1139,9 +1242,9 @@
     </row>
     <row r="6" spans="1:21" ht="140.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
-      <c r="B6" s="10"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1164,9 +1267,9 @@
     </row>
     <row r="7" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
-      <c r="B7" s="10"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1189,9 +1292,9 @@
     </row>
     <row r="8" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1214,9 +1317,9 @@
     </row>
     <row r="9" spans="1:21" ht="105.75" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
-      <c r="B9" s="10"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -1237,10 +1340,12 @@
       <c r="T9" s="10"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="20"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="20" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -1260,10 +1365,12 @@
       <c r="T10" s="10"/>
       <c r="U10" s="5"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="20"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="20" t="s">
+        <v>14</v>
+      </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -1283,10 +1390,12 @@
       <c r="T11" s="10"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
@@ -1306,10 +1415,12 @@
       <c r="T12" s="10"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1470,7 +1581,7 @@
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
@@ -2186,9 +2297,7 @@
     </row>
     <row r="51" spans="1:21" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="1:21" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="C52" s="22"/>
       <c r="D52" s="18"/>
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
@@ -2328,9 +2437,10 @@
       <c r="J65" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B5:B13"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Dokumente/Dhampir-Datenbank.xlsx
+++ b/Dokumente/Dhampir-Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dokumente\1. Projekte\Dhampir\Dokumente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717BDA4F-5029-455D-B5BC-DB8843161AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE22384A-9FEA-4564-BB24-722815FCD5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,7 +355,99 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Jessica, die dunkle Werwolfbraut</t>
+      <t>Dani(el) als Vampir</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+In seiner Vampirgestalt ist sein Charakter sehr aufbrausend, blutdurstig und kaum kontrollierbar. Durch seine noch weiter geschärften Sinne und Muskelkraft kann er sehr schnell potenzielle Opfer (Nicht-Menschliche und Menschliche) erreichen und diese aufnehmen, ohne das Überreste bleiben. Diese Gestalt erreicht er, wen er seinen Körper zuviel Blut zufügt, was das Team dazu brachte mehr über diese Seite an ihm zu erforsch und vielleicht in Zukunft zu beherrschen. Man konnte aber schon bei den ersten Tests erkennen das er in dieser Gestalt andere Wesen einnehmen und seinem  Willen unterwerfen kann, was für kommende Missionen, interessante Verwendungsweisen wären.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Das letzte was er von Akt 13 noch wahr nahm, das ihn auf seinem Heimweg ein kalter Lufthauch und die Gier nach Blut ereilte, nun findet er sich in einem alten Gemäuer eines Gebäudes des Balkan wieder. Seiner Versuche aus diesem Labyrinth waren bislang nich von Erfolg gekrönt und machen ihn nur hoffnungsloser. Gerade hatte man sich als Team zusammengefunden, aber nun war er hier allein mit seinen Erzfeinden, mit denen er wenigstens wie in einem Art Bootcamp trainieren konnte.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Utz, der Mediziner und grüne Hexer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Der Medizinstudent Utz erfuhr früh das der Tod eine schmerzlose Erfahrung sein kann, als Vampire seine Familie und Verwandte bei einem Adventsessen überfiel und verschwinden lies. Um die Macht der Unsterblichkeit zu verstehen und zu benutzen um Rache zu nehmen begann er verschiedenes Wissenstechniken zu erlernen, die er in seiner Schulzeit festigte und im Studium ausbildete. Da bei erregte er die Aufmerksamkeit der regionalen Vampirdynastie die ihn aufgrund seiner Selbstversuche als exzellentes Opfer für ein Blutritual erkannten. Nachdem er Mitglied der Ritter wurde und der magischen Welt begegnete, begann er mit dem Studium der grünen Magie, die sich mit den Kräften der Natur beschäftigt, um den gegnerischen Vampiren ihre Macht zunehmen und auszulöschen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Als Utz auf den Altar da lag, dachte er verzweifelte an die Werwolfgruppe, zu denen er gerade Kontakt aufnehmen konnte. Nachdem er von den jungen Dhampir gerettet wurde, konnte er sich in dessen wachsende Gruppe gut einfinden und mit Ihnen neue und erfolgversprechende Weg finden, Rache wegen seiner Verluste zu nehmen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jessica, die Gothicbraut und dunkle Werwolfbraut</t>
     </r>
     <r>
       <rPr>
@@ -388,45 +480,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Nach Daniels Rückkehr im Rheinland kommt der Werwolfclan zur Entscheidung, sein Leben als Opfer für ihren Wergott zu opfern. Jessica entscheidet daraufhin, den Clan zu verlassen und gemeinsam mit den Rittern den Sie angehört, dieses Opfer zu verhindern, um weiter mit Daniel nach den Fragen der Herkunft, Aufgabe und Zukunftsherausforderungen zu suchen.</t>
+      <t>: Nach Daniels Rückkehr im Rheinland kommt der Werwolfclan zur Entscheidung, sein Leben als Opfer für ihren Wergott zu ermorden. Jessica entscheidet daraufhin, den Clan zu verlassen und gemeinsam mit den Rittern, den Sie nun fest angehört, dieses Opfer zu verhindern, um weiter mit Daniel nach den Fragen der Vergeangenheit, Aufgabe in der Gegenwart und Herausforderungen in der Zukunft zu suchen.</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Utz, der Mediziner und grüne Hexer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-A
-Akt 1: </t>
-    </r>
+    <t xml:space="preserve">Basis der Ritter der Fal
+</t>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Thutmosis, der Ägyptologe und dunkle Hexer</t>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thutmosis, der Ägyptologe und dunkle Hexer (Nekromant)</t>
     </r>
     <r>
       <rPr>
@@ -437,15 +508,36 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-A
-Akt 3:</t>
+In seiner Zeit als Geschichtsprofessor begegnete er vielen dunklen Geschichten und später nach seiner Sperzialisierung zum Ägyptologen noch dunkleren Geheimnissen und Höhlen. Unter seinen Kollegen hat er den Ruf eines verschlossen, herrischen Dozenten und steht in seinem Späterem der Ritter des Fal als Meister für Utz und Jan, aber auch als Ratgeber des Teams stets allen zur Seite. In seinen Expedition konnte er desöfteren schnell das enträtseln von neuen ausgestorbenen Sprachen entdecken und somit neue Forschungsergebnisse präsentieren. In seiner Zeit neben der Forschung entwickelte in verschiedenen Kampfschulen weltweit Kombinationskämpfe die in späteren, insbesondere bei den Rittern gute Dienste leistete. Seine Interessen für Erkundung, Sprachen und Kampftechniken kann er aus stets weiterbilden und in neuen Lehrmethoden festigen. Ausserhalb seines Teamlebens, vollzieht er in einem mysteriösen Kult Rituale des Anubis.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nachdem ihn der Junge Dhampir sein Leben vor dem Blutsauger gerettet hat, verdankt ihn nun sein Leben. Aber er setzte ich auch das Ziel den Tod mit neuen Wissen in seiner Zeit im Team zu besiegen.</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -462,15 +554,37 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-A
-Akt 6:</t>
+Schon in seiner Schulzeit konnte er ein Interesse für Vampire entwickeln, nachdem zufällig mit erlebt hatte wie diese sich an ihren Opfern labben und in ihr menschliches Dasein zurückverwandeln können. Das nahm er sich als Vorbild um seine eigene Mutation in den 
+Begriff zu bekommen und die Geschichte hinter den ganzen zu enträtseln. Im Team Ritter fand er ins besondere Utz und Thutmosis beste Freunde, Ratgeber und Lehrer, die ihn helfen das beste aus seinem Dasein als zuerreichen, was er bei Daniel und Sabrina, die ja auch Mischwesen sind immer sehr gut sich entwickeln sehen kann.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Als er die Ritter bei ihren Aktionen ertappte bekam er direkt den Willen zu ihnen zu gehören. Als die Gruppe die sich gerade kennenlernte, von einem Vampirclan angegriffen wurde, erkannte er aber auch das dieses Team ein neues zuhause sein kann, weil erkannte das er unter ihnen, als kroteskes Wesen nicht alleine ist.</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -487,59 +601,30 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-A
-Akt 12:</t>
-    </r>
-  </si>
-  <si>
+Sie ist Daniels Tante und hilft beim verstecken, der Überreste von den Gegnern vom Team. Aufgrund ihrer städtischen Kontakte und als weiteres Mischwesen, was sich mit den vielen Problem der unterschiedlichen Gruppierungen auskennt, konnte Sie sich schnell im Team beweisen und zu einem unversichtbaren Mitglied werden. Bei ihrer Arbeit im Team bildet sich dadurch schnell eine heftige und bleibende Beziehung mit dem "Gruppenopi" Thutmosis was zu lustigen Storyentwicklung führte.
+</t>
+    </r>
     <r>
       <rPr>
         <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dani(el) als Vampir</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-In seiner Vampirgestalt ist sein Charakter sehr aufbrausend, blutdurstig und kaum kontrollierbar. Durch seine noch weiter geschärften Sinne und Muskelkraft kann er sehr schnell potenzielle Opfer (Nicht-Menschliche und Menschliche) erreichen und diese aufnehmen, ohne das Überreste bleiben. Diese Gestalt erreicht er, wen er seinen Körper zuviel Blut zufügt, was das Team dazu brachte mehr über diese Seite an ihm zu erforsch und vielleicht in Zukunft zu beherrschen. Man konnte aber schon bei den ersten Tests erkennen das er in dieser Gestalt andere Wesen einnehmen und seinem  Willen unterwerfen kann, was für kommende Missionen, interessante Verwendungsweisen wären.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Akt 14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Das letzte was er von Akt 13 noch wahr nahm, das ihn auf seinem Heimweg ein kalter Lufthauch und die Gier nach Blut ereilte, nun findet er sich in einem alten Gemäuer eines Gebäudes des Balkan wieder. Seiner Versuche aus diesem Labyrinth waren bislang nich von Erfolg gekrönt und machen ihn nur hoffnungsloser. Gerade hatte man sich als Team zusammengefunden, aber nun war er hier allein mit seinen Erzfeinden, mit denen er wenigstens wie in einem Art Bootcamp trainieren konnte.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis der Ritter der Nacht
-</t>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Akt 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nachdem Sie endlich herausfand was ihr Neffe da so treibt, wurde Sie von deren Gegnern erwischt, wobei ihre Kräfte eine starke Unterstützung waren. Sie hatte geahnt welche Freude dieser Auftritt bei Daniel ausrichten würde. Dieser Anblick sollte ihr für immer im Gedächtnis bleiben.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1130,7 +1215,7 @@
   <cols>
     <col min="1" max="1" width="29.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="229.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="242.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -1216,7 +1301,7 @@
     <row r="5" spans="1:21" ht="166.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
       <c r="B5" s="23" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>9</v>
@@ -1269,7 +1354,7 @@
       <c r="A7" s="16"/>
       <c r="B7" s="24"/>
       <c r="C7" s="20" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1319,7 +1404,7 @@
       <c r="A9" s="16"/>
       <c r="B9" s="24"/>
       <c r="C9" s="20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -1340,7 +1425,7 @@
       <c r="T9" s="10"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="24"/>
       <c r="C10" s="20" t="s">
@@ -1365,11 +1450,11 @@
       <c r="T10" s="10"/>
       <c r="U10" s="5"/>
     </row>
-    <row r="11" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="90.75" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="24"/>
       <c r="C11" s="20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -1390,11 +1475,11 @@
       <c r="T11" s="10"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="105.75" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="24"/>
       <c r="C12" s="20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1415,11 +1500,11 @@
       <c r="T12" s="10"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="75.75" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="24"/>
       <c r="C13" s="20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
